--- a/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Univariado/Fichas/indice_fichas.xlsx
+++ b/DATA/MASTER/C10_MASTER/Resultados_EDA/Analisis_Univariado/Fichas/indice_fichas.xlsx
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100</v>
+        <v>63.64</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -918,17 +918,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>No definido</t>
+          <t>No documentado en C09/C10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No definida</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -948,17 +948,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>No definido</t>
+          <t>No documentado en C09/C10</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>No definida</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E18" t="n">
